--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП филиал Луганск на .xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП филиал Луганск на .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A7F1879-CF5C-4FD0-9665-B55B58D74CD7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B739EC-FBAC-479C-B79F-5AF3E48545F4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$165</definedName>
-    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$601</definedName>
-    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$601</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$164</definedName>
+    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$600</definedName>
+    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$600</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -332,7 +332,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="227">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -6214,7 +6214,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BO1689"/>
+  <dimension ref="A1:BO1688"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -14550,7 +14550,7 @@
     </row>
     <row r="106" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A106" s="123" t="str">
-        <f t="shared" ref="A106:A140" si="20">RIGHT(D106,4)</f>
+        <f t="shared" ref="A106:A139" si="20">RIGHT(D106,4)</f>
         <v>3582</v>
       </c>
       <c r="B106" s="53" t="s">
@@ -16539,7 +16539,7 @@
         <v>0.15</v>
       </c>
       <c r="G129" s="23">
-        <f t="shared" ref="G129:G139" si="26">E129*F129</f>
+        <f t="shared" ref="G129:G138" si="26">E129*F129</f>
         <v>0</v>
       </c>
       <c r="H129" s="14">
@@ -17211,27 +17211,27 @@
     <row r="137" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="123" t="str">
         <f t="shared" si="20"/>
-        <v>6557</v>
+        <v>5679</v>
       </c>
       <c r="B137" s="53" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C137" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D137" s="51">
-        <v>1001200756557</v>
+        <v>1001190765679</v>
       </c>
       <c r="E137" s="24"/>
       <c r="F137" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G137" s="23">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H137" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I137" s="14">
         <v>60</v>
@@ -17297,27 +17297,27 @@
     <row r="138" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="123" t="str">
         <f t="shared" si="20"/>
-        <v>5679</v>
+        <v>5677</v>
       </c>
       <c r="B138" s="53" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C138" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D138" s="51">
-        <v>1001190765679</v>
+        <v>1001190715677</v>
       </c>
       <c r="E138" s="24"/>
       <c r="F138" s="23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G138" s="23">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H138" s="14">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I138" s="14">
         <v>60</v>
@@ -17380,30 +17380,30 @@
       <c r="BN138"/>
       <c r="BO138"/>
     </row>
-    <row r="139" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="123" t="str">
         <f t="shared" si="20"/>
-        <v>5677</v>
+        <v>7414</v>
       </c>
       <c r="B139" s="53" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C139" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D139" s="51">
-        <v>1001190715677</v>
+        <v>1001204447414</v>
       </c>
       <c r="E139" s="24"/>
       <c r="F139" s="23">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G139" s="23">
-        <f t="shared" si="26"/>
+        <f>E139</f>
         <v>0</v>
       </c>
       <c r="H139" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I139" s="14">
         <v>60</v>
@@ -17466,35 +17466,21 @@
       <c r="BN139"/>
       <c r="BO139"/>
     </row>
-    <row r="140" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="123" t="str">
-        <f t="shared" si="20"/>
-        <v>7414</v>
-      </c>
-      <c r="B140" s="53" t="s">
-        <v>138</v>
-      </c>
-      <c r="C140" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D140" s="51">
-        <v>1001204447414</v>
-      </c>
+    <row r="140" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B140" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C140" s="42"/>
+      <c r="D140" s="42"/>
       <c r="E140" s="24"/>
-      <c r="F140" s="23">
-        <v>1</v>
-      </c>
-      <c r="G140" s="23">
-        <f>E140</f>
-        <v>0</v>
-      </c>
-      <c r="H140" s="14">
-        <v>8</v>
-      </c>
-      <c r="I140" s="14">
-        <v>60</v>
-      </c>
-      <c r="J140" s="29"/>
+      <c r="F140" s="41"/>
+      <c r="G140" s="42"/>
+      <c r="H140" s="42"/>
+      <c r="I140" s="42"/>
+      <c r="J140" s="43"/>
       <c r="L140"/>
       <c r="M140"/>
       <c r="N140"/>
@@ -17552,21 +17538,35 @@
       <c r="BN140"/>
       <c r="BO140"/>
     </row>
-    <row r="141" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B141" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="C141" s="42"/>
-      <c r="D141" s="42"/>
+    <row r="141" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="123" t="str">
+        <f t="shared" ref="A141:A150" si="27">RIGHT(D141,4)</f>
+        <v>4584</v>
+      </c>
+      <c r="B141" s="98" t="s">
+        <v>213</v>
+      </c>
+      <c r="C141" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="D141" s="130">
+        <v>1001092674584</v>
+      </c>
       <c r="E141" s="24"/>
-      <c r="F141" s="41"/>
-      <c r="G141" s="42"/>
-      <c r="H141" s="42"/>
-      <c r="I141" s="42"/>
-      <c r="J141" s="43"/>
+      <c r="F141" s="23">
+        <v>2.5</v>
+      </c>
+      <c r="G141" s="23">
+        <f>E141</f>
+        <v>0</v>
+      </c>
+      <c r="H141" s="14">
+        <v>7.5</v>
+      </c>
+      <c r="I141" s="14">
+        <v>60</v>
+      </c>
+      <c r="J141" s="29"/>
       <c r="L141"/>
       <c r="M141"/>
       <c r="N141"/>
@@ -17624,33 +17624,33 @@
       <c r="BN141"/>
       <c r="BO141"/>
     </row>
-    <row r="142" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="123" t="str">
-        <f t="shared" ref="A142:A151" si="27">RIGHT(D142,4)</f>
-        <v>4584</v>
+        <f t="shared" si="27"/>
+        <v>6495</v>
       </c>
       <c r="B142" s="98" t="s">
-        <v>213</v>
+        <v>95</v>
       </c>
       <c r="C142" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D142" s="130">
-        <v>1001092674584</v>
+        <v>20</v>
+      </c>
+      <c r="D142" s="51">
+        <v>1001092436495</v>
       </c>
       <c r="E142" s="24"/>
-      <c r="F142" s="23">
-        <v>2.5</v>
+      <c r="F142" s="124">
+        <v>0.3</v>
       </c>
       <c r="G142" s="23">
-        <f>E142</f>
+        <f>E142*F142</f>
         <v>0</v>
       </c>
-      <c r="H142" s="14">
-        <v>7.5</v>
-      </c>
-      <c r="I142" s="14">
-        <v>60</v>
+      <c r="H142" s="29">
+        <v>1.8</v>
+      </c>
+      <c r="I142" s="29">
+        <v>45</v>
       </c>
       <c r="J142" s="29"/>
       <c r="L142"/>
@@ -17713,27 +17713,27 @@
     <row r="143" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="123" t="str">
         <f t="shared" si="27"/>
-        <v>6495</v>
-      </c>
-      <c r="B143" s="98" t="s">
-        <v>95</v>
+        <v>6470</v>
+      </c>
+      <c r="B143" s="131" t="s">
+        <v>116</v>
       </c>
       <c r="C143" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D143" s="51">
-        <v>1001092436495</v>
+        <v>1001092436470</v>
       </c>
       <c r="E143" s="24"/>
       <c r="F143" s="124">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="G143" s="23">
-        <f>E143*F143</f>
+        <f t="shared" ref="G143:G144" si="28">E143</f>
         <v>0</v>
       </c>
       <c r="H143" s="29">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="I143" s="29">
         <v>45</v>
@@ -17799,30 +17799,30 @@
     <row r="144" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="123" t="str">
         <f t="shared" si="27"/>
-        <v>6470</v>
+        <v>5452</v>
       </c>
       <c r="B144" s="131" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="C144" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D144" s="51">
-        <v>1001092436470</v>
+        <v>1001092485452</v>
       </c>
       <c r="E144" s="24"/>
       <c r="F144" s="124">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="G144" s="23">
-        <f t="shared" ref="G144:G145" si="28">E144</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H144" s="29">
-        <v>4.8</v>
+        <v>4.05</v>
       </c>
       <c r="I144" s="29">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J144" s="29"/>
       <c r="L144"/>
@@ -17885,27 +17885,27 @@
     <row r="145" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="123" t="str">
         <f t="shared" si="27"/>
-        <v>5452</v>
+        <v>3215</v>
       </c>
       <c r="B145" s="131" t="s">
-        <v>93</v>
+        <v>214</v>
       </c>
       <c r="C145" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D145" s="51">
-        <v>1001092485452</v>
+        <v>1001094053215</v>
       </c>
       <c r="E145" s="24"/>
       <c r="F145" s="124">
-        <v>1.35</v>
+        <v>0.4</v>
       </c>
       <c r="G145" s="23">
-        <f t="shared" si="28"/>
+        <f>E145*F145</f>
         <v>0</v>
       </c>
       <c r="H145" s="29">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="I145" s="29">
         <v>60</v>
@@ -17971,27 +17971,27 @@
     <row r="146" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="123" t="str">
         <f t="shared" si="27"/>
-        <v>3215</v>
+        <v>6866</v>
       </c>
       <c r="B146" s="131" t="s">
-        <v>214</v>
+        <v>92</v>
       </c>
       <c r="C146" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D146" s="51">
-        <v>1001094053215</v>
+        <v>1001095716866</v>
       </c>
       <c r="E146" s="24"/>
       <c r="F146" s="124">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G146" s="23">
-        <f>E146*F146</f>
+        <f>E146</f>
         <v>0</v>
       </c>
       <c r="H146" s="29">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I146" s="29">
         <v>60</v>
@@ -18054,30 +18054,30 @@
       <c r="BN146"/>
       <c r="BO146"/>
     </row>
-    <row r="147" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="123" t="str">
         <f t="shared" si="27"/>
-        <v>6866</v>
-      </c>
-      <c r="B147" s="131" t="s">
-        <v>92</v>
+        <v>5495</v>
+      </c>
+      <c r="B147" s="53" t="s">
+        <v>94</v>
       </c>
       <c r="C147" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D147" s="51">
-        <v>1001095716866</v>
+        <v>20</v>
+      </c>
+      <c r="D147" s="132">
+        <v>1001093345495</v>
       </c>
       <c r="E147" s="24"/>
       <c r="F147" s="124">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G147" s="23">
-        <f>E147</f>
+        <f t="shared" ref="G147:G149" si="29">E147*F147</f>
         <v>0</v>
       </c>
       <c r="H147" s="29">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="I147" s="29">
         <v>60</v>
@@ -18143,30 +18143,30 @@
     <row r="148" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="123" t="str">
         <f t="shared" si="27"/>
-        <v>5495</v>
+        <v>7377</v>
       </c>
       <c r="B148" s="53" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="C148" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D148" s="132">
-        <v>1001093345495</v>
+        <v>1001095027377</v>
       </c>
       <c r="E148" s="24"/>
       <c r="F148" s="124">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G148" s="23">
-        <f t="shared" ref="G148:G150" si="29">E148*F148</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H148" s="29">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="I148" s="29">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J148" s="29"/>
       <c r="L148"/>
@@ -18229,27 +18229,27 @@
     <row r="149" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="123" t="str">
         <f t="shared" si="27"/>
-        <v>7377</v>
+        <v>6925</v>
       </c>
       <c r="B149" s="53" t="s">
-        <v>117</v>
+        <v>215</v>
       </c>
       <c r="C149" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D149" s="132">
-        <v>1001095027377</v>
+        <v>1001095226925</v>
       </c>
       <c r="E149" s="24"/>
       <c r="F149" s="124">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="G149" s="23">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H149" s="29">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="I149" s="29">
         <v>45</v>
@@ -18312,33 +18312,33 @@
       <c r="BN149"/>
       <c r="BO149"/>
     </row>
-    <row r="150" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="123" t="str">
         <f t="shared" si="27"/>
-        <v>6925</v>
+        <v>6025</v>
       </c>
       <c r="B150" s="53" t="s">
-        <v>215</v>
+        <v>118</v>
       </c>
       <c r="C150" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D150" s="132">
-        <v>1001095226925</v>
+        <v>1001094966025</v>
       </c>
       <c r="E150" s="24"/>
       <c r="F150" s="124">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="G150" s="23">
-        <f t="shared" si="29"/>
+        <f>E150</f>
         <v>0</v>
       </c>
       <c r="H150" s="29">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="I150" s="29">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J150" s="29"/>
       <c r="L150"/>
@@ -18398,35 +18398,21 @@
       <c r="BN150"/>
       <c r="BO150"/>
     </row>
-    <row r="151" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="123" t="str">
-        <f t="shared" si="27"/>
-        <v>6025</v>
-      </c>
-      <c r="B151" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="C151" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D151" s="132">
-        <v>1001094966025</v>
-      </c>
+    <row r="151" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B151" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="C151" s="42"/>
+      <c r="D151" s="42"/>
       <c r="E151" s="24"/>
-      <c r="F151" s="124">
-        <v>3</v>
-      </c>
-      <c r="G151" s="23">
-        <f>E151</f>
-        <v>0</v>
-      </c>
-      <c r="H151" s="29">
-        <v>6</v>
-      </c>
-      <c r="I151" s="29">
-        <v>60</v>
-      </c>
-      <c r="J151" s="29"/>
+      <c r="F151" s="41"/>
+      <c r="G151" s="42"/>
+      <c r="H151" s="42"/>
+      <c r="I151" s="42"/>
+      <c r="J151" s="43"/>
       <c r="L151"/>
       <c r="M151"/>
       <c r="N151"/>
@@ -18484,21 +18470,35 @@
       <c r="BN151"/>
       <c r="BO151"/>
     </row>
-    <row r="152" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B152" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="C152" s="42"/>
-      <c r="D152" s="42"/>
+    <row r="152" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="123" t="str">
+        <f t="shared" ref="A152:A163" si="30">RIGHT(D152,4)</f>
+        <v>7090</v>
+      </c>
+      <c r="B152" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="C152" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D152" s="51">
+        <v>1001084217090</v>
+      </c>
       <c r="E152" s="24"/>
-      <c r="F152" s="41"/>
-      <c r="G152" s="42"/>
-      <c r="H152" s="42"/>
-      <c r="I152" s="42"/>
-      <c r="J152" s="43"/>
+      <c r="F152" s="23">
+        <v>0.3</v>
+      </c>
+      <c r="G152" s="23">
+        <f t="shared" ref="G152:G153" si="31">E152*F152</f>
+        <v>0</v>
+      </c>
+      <c r="H152" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="I152" s="14">
+        <v>50</v>
+      </c>
+      <c r="J152" s="29"/>
       <c r="L152"/>
       <c r="M152"/>
       <c r="N152"/>
@@ -18556,26 +18556,26 @@
       <c r="BN152"/>
       <c r="BO152"/>
     </row>
-    <row r="153" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="123" t="str">
-        <f t="shared" ref="A153:A164" si="30">RIGHT(D153,4)</f>
-        <v>7090</v>
+        <f t="shared" si="30"/>
+        <v>7187</v>
       </c>
       <c r="B153" s="35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C153" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D153" s="51">
-        <v>1001084217090</v>
+        <v>1001085637187</v>
       </c>
       <c r="E153" s="24"/>
       <c r="F153" s="23">
         <v>0.3</v>
       </c>
       <c r="G153" s="23">
-        <f t="shared" ref="G153:G154" si="31">E153*F153</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H153" s="14">
@@ -18645,30 +18645,30 @@
     <row r="154" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="123" t="str">
         <f t="shared" si="30"/>
-        <v>7187</v>
+        <v>6620</v>
       </c>
       <c r="B154" s="35" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C154" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D154" s="51">
-        <v>1001085637187</v>
+        <v>1001081596620</v>
       </c>
       <c r="E154" s="24"/>
       <c r="F154" s="23">
-        <v>0.3</v>
+        <v>1.05</v>
       </c>
       <c r="G154" s="23">
-        <f t="shared" si="31"/>
+        <f>E154</f>
         <v>0</v>
       </c>
       <c r="H154" s="14">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="I154" s="14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J154" s="29"/>
       <c r="L154"/>
@@ -18731,31 +18731,25 @@
     <row r="155" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="123" t="str">
         <f t="shared" si="30"/>
-        <v>6620</v>
+        <v>6008</v>
       </c>
       <c r="B155" s="35" t="s">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c r="C155" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D155" s="51">
-        <v>1001081596620</v>
+        <v>1001084856008</v>
       </c>
       <c r="E155" s="24"/>
-      <c r="F155" s="23">
-        <v>1.05</v>
-      </c>
+      <c r="F155" s="23"/>
       <c r="G155" s="23">
         <f>E155</f>
         <v>0</v>
       </c>
-      <c r="H155" s="14">
-        <v>3.15</v>
-      </c>
-      <c r="I155" s="14">
-        <v>30</v>
-      </c>
+      <c r="H155" s="14"/>
+      <c r="I155" s="14"/>
       <c r="J155" s="29"/>
       <c r="L155"/>
       <c r="M155"/>
@@ -18817,25 +18811,31 @@
     <row r="156" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="123" t="str">
         <f t="shared" si="30"/>
-        <v>6008</v>
+        <v>7103</v>
       </c>
       <c r="B156" s="35" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="C156" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D156" s="51">
-        <v>1001084856008</v>
+        <v>1001223297103</v>
       </c>
       <c r="E156" s="24"/>
-      <c r="F156" s="23"/>
+      <c r="F156" s="23">
+        <v>0.18</v>
+      </c>
       <c r="G156" s="23">
-        <f>E156</f>
+        <f t="shared" ref="G156:G163" si="32">E156*F156</f>
         <v>0</v>
       </c>
-      <c r="H156" s="14"/>
-      <c r="I156" s="14"/>
+      <c r="H156" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="I156" s="14">
+        <v>50</v>
+      </c>
       <c r="J156" s="29"/>
       <c r="L156"/>
       <c r="M156"/>
@@ -18896,28 +18896,28 @@
     </row>
     <row r="157" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="123" t="str">
-        <f t="shared" si="30"/>
-        <v>7103</v>
+        <f>RIGHT(D157,4)</f>
+        <v>7092</v>
       </c>
       <c r="B157" s="35" t="s">
-        <v>216</v>
+        <v>78</v>
       </c>
       <c r="C157" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D157" s="51">
-        <v>1001223297103</v>
+        <v>1001223297092</v>
       </c>
       <c r="E157" s="24"/>
       <c r="F157" s="23">
-        <v>0.18</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G157" s="23">
-        <f t="shared" ref="G157:G164" si="32">E157*F157</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H157" s="14">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="I157" s="14">
         <v>50</v>
@@ -18982,31 +18982,31 @@
     </row>
     <row r="158" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="123" t="str">
-        <f>RIGHT(D158,4)</f>
-        <v>7092</v>
+        <f t="shared" si="30"/>
+        <v>6228</v>
       </c>
       <c r="B158" s="35" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C158" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D158" s="51">
-        <v>1001223297092</v>
+        <v>1001225416228</v>
       </c>
       <c r="E158" s="24"/>
       <c r="F158" s="23">
-        <v>0.14000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="G158" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H158" s="14">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="I158" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J158" s="29"/>
       <c r="L158"/>
@@ -19069,27 +19069,27 @@
     <row r="159" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="123" t="str">
         <f t="shared" si="30"/>
-        <v>6228</v>
+        <v>6448</v>
       </c>
       <c r="B159" s="35" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="C159" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D159" s="51">
-        <v>1001225416228</v>
+        <v>1001234146448</v>
       </c>
       <c r="E159" s="24"/>
       <c r="F159" s="23">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G159" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H159" s="14">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I159" s="14">
         <v>45</v>
@@ -19155,27 +19155,27 @@
     <row r="160" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="123" t="str">
         <f t="shared" si="30"/>
-        <v>6448</v>
+        <v>6208</v>
       </c>
       <c r="B160" s="35" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="C160" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D160" s="51">
-        <v>1001234146448</v>
+        <v>1001220226208</v>
       </c>
       <c r="E160" s="24"/>
       <c r="F160" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G160" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H160" s="14">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I160" s="14">
         <v>45</v>
@@ -19241,30 +19241,30 @@
     <row r="161" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="123" t="str">
         <f t="shared" si="30"/>
-        <v>6208</v>
+        <v>6754</v>
       </c>
       <c r="B161" s="35" t="s">
-        <v>99</v>
+        <v>217</v>
       </c>
       <c r="C161" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D161" s="51">
-        <v>1001220226208</v>
+        <v>1001225406754</v>
       </c>
       <c r="E161" s="24"/>
       <c r="F161" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G161" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H161" s="14">
-        <v>1.5</v>
+        <v>0.72</v>
       </c>
       <c r="I161" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J161" s="29"/>
       <c r="L161"/>
@@ -19327,30 +19327,30 @@
     <row r="162" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="123" t="str">
         <f t="shared" si="30"/>
-        <v>6754</v>
+        <v>6279</v>
       </c>
       <c r="B162" s="35" t="s">
-        <v>217</v>
+        <v>98</v>
       </c>
       <c r="C162" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D162" s="51">
-        <v>1001225406754</v>
+        <v>1001220286279</v>
       </c>
       <c r="E162" s="24"/>
       <c r="F162" s="23">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G162" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H162" s="14">
-        <v>0.72</v>
+        <v>1.2</v>
       </c>
       <c r="I162" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J162" s="29"/>
       <c r="L162"/>
@@ -19410,33 +19410,33 @@
       <c r="BN162"/>
       <c r="BO162"/>
     </row>
-    <row r="163" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="123" t="str">
         <f t="shared" si="30"/>
-        <v>6279</v>
+        <v>7288</v>
       </c>
       <c r="B163" s="35" t="s">
-        <v>98</v>
+        <v>192</v>
       </c>
       <c r="C163" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D163" s="51">
-        <v>1001220286279</v>
+        <v>1001223907288</v>
       </c>
       <c r="E163" s="24"/>
       <c r="F163" s="23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G163" s="23">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H163" s="14">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I163" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J163" s="29"/>
       <c r="L163"/>
@@ -19496,35 +19496,25 @@
       <c r="BN163"/>
       <c r="BO163"/>
     </row>
-    <row r="164" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="123" t="str">
-        <f t="shared" si="30"/>
-        <v>7288</v>
-      </c>
-      <c r="B164" s="35" t="s">
-        <v>192</v>
-      </c>
-      <c r="C164" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D164" s="51">
-        <v>1001223907288</v>
-      </c>
-      <c r="E164" s="24"/>
-      <c r="F164" s="23">
-        <v>0.1</v>
-      </c>
-      <c r="G164" s="23">
-        <f t="shared" si="32"/>
+    <row r="164" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="48"/>
+      <c r="B164" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="C164" s="16"/>
+      <c r="D164" s="36"/>
+      <c r="E164" s="17">
+        <f>SUM(E10:E163)</f>
         <v>0</v>
       </c>
-      <c r="H164" s="14">
-        <v>1</v>
-      </c>
-      <c r="I164" s="14">
-        <v>60</v>
-      </c>
-      <c r="J164" s="29"/>
+      <c r="F164" s="17"/>
+      <c r="G164" s="17">
+        <f>SUM(G11:G163)</f>
+        <v>0</v>
+      </c>
+      <c r="H164" s="17"/>
+      <c r="I164" s="17"/>
+      <c r="J164" s="17"/>
       <c r="L164"/>
       <c r="M164"/>
       <c r="N164"/>
@@ -19582,83 +19572,17 @@
       <c r="BN164"/>
       <c r="BO164"/>
     </row>
-    <row r="165" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="48"/>
-      <c r="B165" s="45" t="s">
-        <v>102</v>
-      </c>
-      <c r="C165" s="16"/>
-      <c r="D165" s="36"/>
-      <c r="E165" s="17">
-        <f>SUM(E10:E164)</f>
-        <v>0</v>
-      </c>
-      <c r="F165" s="17"/>
-      <c r="G165" s="17">
-        <f>SUM(G11:G164)</f>
-        <v>0</v>
-      </c>
-      <c r="H165" s="17"/>
-      <c r="I165" s="17"/>
-      <c r="J165" s="17"/>
-      <c r="L165"/>
-      <c r="M165"/>
-      <c r="N165"/>
-      <c r="O165"/>
-      <c r="P165"/>
-      <c r="Q165"/>
-      <c r="R165"/>
-      <c r="S165"/>
-      <c r="T165"/>
-      <c r="U165"/>
-      <c r="V165"/>
-      <c r="W165"/>
-      <c r="X165"/>
-      <c r="Y165"/>
-      <c r="Z165"/>
-      <c r="AA165"/>
-      <c r="AB165"/>
-      <c r="AC165"/>
-      <c r="AD165"/>
-      <c r="AE165"/>
-      <c r="AF165"/>
-      <c r="AG165"/>
-      <c r="AH165"/>
-      <c r="AI165"/>
-      <c r="AJ165"/>
-      <c r="AK165"/>
-      <c r="AL165"/>
-      <c r="AM165"/>
-      <c r="AN165"/>
-      <c r="AO165"/>
-      <c r="AP165"/>
-      <c r="AQ165"/>
-      <c r="AR165"/>
-      <c r="AS165"/>
-      <c r="AT165"/>
-      <c r="AU165"/>
-      <c r="AV165"/>
-      <c r="AW165"/>
-      <c r="AX165"/>
-      <c r="AY165"/>
-      <c r="AZ165"/>
-      <c r="BA165"/>
-      <c r="BB165"/>
-      <c r="BC165"/>
-      <c r="BD165"/>
-      <c r="BE165"/>
-      <c r="BF165"/>
-      <c r="BG165"/>
-      <c r="BH165"/>
-      <c r="BI165"/>
-      <c r="BJ165"/>
-      <c r="BK165"/>
-      <c r="BL165"/>
-      <c r="BM165"/>
-      <c r="BN165"/>
-      <c r="BO165"/>
-    </row>
-    <row r="166" spans="1:67" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:67" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B165" s="37"/>
+      <c r="C165" s="18"/>
+      <c r="D165" s="40"/>
+      <c r="F165" s="19"/>
+      <c r="G165" s="19"/>
+      <c r="H165" s="20"/>
+      <c r="I165" s="20"/>
+      <c r="J165" s="21"/>
+    </row>
+    <row r="166" spans="1:67" x14ac:dyDescent="0.25">
       <c r="B166" s="37"/>
       <c r="C166" s="18"/>
       <c r="D166" s="40"/>
@@ -19710,12 +19634,13 @@
     </row>
     <row r="171" spans="1:67" x14ac:dyDescent="0.25">
       <c r="B171" s="37"/>
-      <c r="C171" s="18"/>
-      <c r="D171" s="40"/>
-      <c r="F171" s="19"/>
-      <c r="G171" s="19"/>
-      <c r="H171" s="20"/>
-      <c r="I171" s="20"/>
+      <c r="C171" s="55"/>
+      <c r="D171" s="56"/>
+      <c r="E171" s="57"/>
+      <c r="F171" s="58"/>
+      <c r="G171" s="58"/>
+      <c r="H171" s="59"/>
+      <c r="I171" s="59"/>
       <c r="J171" s="21"/>
     </row>
     <row r="172" spans="1:67" x14ac:dyDescent="0.25">
@@ -19732,23 +19657,22 @@
     <row r="173" spans="1:67" x14ac:dyDescent="0.25">
       <c r="B173" s="37"/>
       <c r="C173" s="55"/>
-      <c r="D173" s="56"/>
-      <c r="E173" s="57"/>
-      <c r="F173" s="58"/>
-      <c r="G173" s="58"/>
-      <c r="H173" s="59"/>
-      <c r="I173" s="59"/>
+      <c r="D173" s="60"/>
+      <c r="E173" s="61"/>
+      <c r="F173" s="60"/>
+      <c r="G173" s="62"/>
+      <c r="H173" s="63"/>
+      <c r="I173" s="64"/>
       <c r="J173" s="21"/>
     </row>
     <row r="174" spans="1:67" x14ac:dyDescent="0.25">
       <c r="B174" s="37"/>
-      <c r="C174" s="55"/>
-      <c r="D174" s="60"/>
-      <c r="E174" s="61"/>
-      <c r="F174" s="60"/>
-      <c r="G174" s="62"/>
-      <c r="H174" s="63"/>
-      <c r="I174" s="64"/>
+      <c r="C174" s="18"/>
+      <c r="D174" s="40"/>
+      <c r="F174" s="19"/>
+      <c r="G174" s="19"/>
+      <c r="H174" s="20"/>
+      <c r="I174" s="20"/>
       <c r="J174" s="21"/>
     </row>
     <row r="175" spans="1:67" x14ac:dyDescent="0.25">
@@ -34891,23 +34815,13 @@
       <c r="I1688" s="20"/>
       <c r="J1688" s="21"/>
     </row>
-    <row r="1689" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B1689" s="37"/>
-      <c r="C1689" s="18"/>
-      <c r="D1689" s="40"/>
-      <c r="F1689" s="19"/>
-      <c r="G1689" s="19"/>
-      <c r="H1689" s="20"/>
-      <c r="I1689" s="20"/>
-      <c r="J1689" s="21"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A9:J165" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J164" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D174">
+  <conditionalFormatting sqref="D173">
     <cfRule type="duplicateValues" dxfId="384" priority="1"/>
     <cfRule type="duplicateValues" dxfId="383" priority="2"/>
     <cfRule type="duplicateValues" dxfId="382" priority="3"/>
@@ -34919,7 +34833,7 @@
     <cfRule type="duplicateValues" dxfId="376" priority="10"/>
     <cfRule type="duplicateValues" dxfId="375" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D174">
+  <conditionalFormatting sqref="D173">
     <cfRule type="duplicateValues" dxfId="374" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
